--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>包含嚼檳榔資料來源代碼之值集。（provisional，隨 CS-BetelNutInfoSource 待官方確認）</t>
+    <t>【主管機關：國民健康署】包含嚼檳榔資料來源代碼之值集。（provisional，隨 CS-BetelNutInfoSource 待官方確認）</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-BetelNutInfoSource.xlsx
+++ b/ValueSet-VS-BetelNutInfoSource.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
